--- a/ArgoBooks/Resources/SampleCompanyData.xlsx
+++ b/ArgoBooks/Resources/SampleCompanyData.xlsx
@@ -551,17 +551,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>ON</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>78701</t>
+          <t>M5H 2N2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -616,17 +616,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Edinburgh</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>Edinburgh</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>77002</t>
+          <t>EH1 1BB</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -681,17 +681,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Brisbane</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>QLD</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>75201</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -746,17 +746,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Vancouver</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>BC</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>78205</t>
+          <t>V6B 1A1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -806,17 +806,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>München</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>78702</t>
+          <t>80331</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -871,17 +871,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>Auvergne-Rhône-Alpes</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>77003</t>
+          <t>69002</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -936,17 +936,17 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Dublin</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>Dublin</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>75202</t>
+          <t>D02 XY45</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1001,17 +1001,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Amsterdam</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>Noord-Holland</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>78703</t>
+          <t>1012 AB</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1066,17 +1066,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Auckland</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>Auckland</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>78206</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1191,17 +1191,17 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Calgary</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>78704</t>
+          <t>T2P 1J9</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1256,17 +1256,17 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Glasgow</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>Glasgow</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>75203</t>
+          <t>G1 1XW</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1321,17 +1321,17 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>77005</t>
+          <t>08007</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1386,17 +1386,17 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>78705</t>
+          <t>41121</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1451,17 +1451,17 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>78207</t>
+          <t>8001</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -10151,17 +10151,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Round Rock</t>
+          <t>Mississauga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>ON</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>78682</t>
+          <t>L5N 1W1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -10208,17 +10208,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Irvine</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>92612</t>
+          <t>AB10 1XG</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -10265,17 +10265,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Clearwater</t>
+          <t>Hamburg</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>Hamburg</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>33760</t>
+          <t>20095</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -10322,17 +10322,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>San Jose</t>
+          <t>Sydney</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>NSW</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>95134</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -10379,17 +10379,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Redmond</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>WA</t>
+          <t>Pays de la Loire</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>98052</t>
+          <t>44000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -10436,17 +10436,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Palo Alto</t>
+          <t>Rotterdam</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>Zuid-Holland</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>94304</t>
+          <t>3011 AA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -10550,17 +10550,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Boca Raton</t>
+          <t>Yokohama</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>Kanagawa</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>33496</t>
+          <t>220-0012</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">

--- a/ArgoBooks/Resources/SampleCompanyData.xlsx
+++ b/ArgoBooks/Resources/SampleCompanyData.xlsx
@@ -17,15 +17,16 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Revenue" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Expenses" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inventory" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stock Adjustments" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Purchase Orders" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rental Inventory" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rental Records" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recurring Invoices" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Purchase Order Line Items" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Returns" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lost Damaged" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assets" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inventory" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stock Adjustments" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Purchase Orders" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rental Inventory" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rental Records" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recurring Invoices" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Purchase Order Line Items" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Returns" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lost Damaged" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -5412,7 +5413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J36"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1">
@@ -6963,6 +6964,109 @@
       </c>
       <c r="J36" t="n">
         <v>1.12</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>PUR-2025-036</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2025-01-08</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>SUP-001</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Label Printer</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F37" t="n">
+        <v>60</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1260</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Credit Card</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>PUR-2025-037</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Delivery Van</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>32000</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1600</v>
+      </c>
+      <c r="G38" t="n">
+        <v>33600</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Bank Transfer</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>PUR-2025-038</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>SUP-001</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Staff Laptops</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>3200</v>
+      </c>
+      <c r="F39" t="n">
+        <v>160</v>
+      </c>
+      <c r="G39" t="n">
+        <v>3360</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Credit Card</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -6976,8 +7080,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
+  <dimension ref="A1:O7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -6987,547 +7108,355 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Product ID</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Location ID</t>
+          <t>Type</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>In Stock</t>
+          <t>Purchase Date</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Reserved</t>
+          <t>Cost</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Reorder Point</t>
+          <t>Currency</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Unit Cost</t>
+          <t>Expense ID</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Last Updated</t>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Useful Life (Years)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Rate %</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>CRA Class</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Disposed Date</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Disposal</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Sale Price</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>INV-ITM-001</t>
+          <t>AST-001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PRD-001</t>
+          <t>Storage lot</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>LOC-001</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>12</v>
+          <t>Land</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2021-06-01</t>
+        </is>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G2" t="n">
-        <v>899</v>
+        <v>60000</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>StraightLine</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Owned before the business started using Argo Books</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>INV-ITM-002</t>
+          <t>AST-002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PRD-002</t>
+          <t>Label printer</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>LOC-001</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>6</v>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2025-01-08</t>
+        </is>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" t="n">
-        <v>3</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1349</v>
+        <v>1200</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>PUR-2025-036</t>
+        </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>DecliningBalance</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Sold</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>700</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Replaced by a faster model</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>INV-ITM-003</t>
+          <t>AST-003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PRD-003</t>
+          <t>Delivery van</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>LOC-001</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>4</v>
+          <t>Vehicle</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>4</v>
-      </c>
-      <c r="G4" t="n">
-        <v>849</v>
+        <v>32000</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>PUR-2025-037</t>
+        </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>DecliningBalance</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>INV-ITM-004</t>
+          <t>AST-004</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PRD-004</t>
+          <t>Executive desk</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>LOC-001</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>8</v>
+          <t>FurnitureAndFixtures</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F5" t="n">
-        <v>5</v>
-      </c>
-      <c r="G5" t="n">
-        <v>699</v>
+        <v>3048.53</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>PUR-2025-021</t>
+        </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>DecliningBalance</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>INV-ITM-005</t>
+          <t>AST-005</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PRD-005</t>
+          <t>Staff laptops</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>LOC-001</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>5</v>
+          <t>ComputerEquipment</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2025-10-20</t>
+        </is>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" t="n">
-        <v>2</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1999</v>
+        <v>3200</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>PUR-2025-038</t>
+        </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>DecliningBalance</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>50</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>INV-ITM-006</t>
+          <t>AST-006</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PRD-006</t>
+          <t>Ergonomic office chairs</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>LOC-001</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>8</v>
+          <t>FurnitureAndFixtures</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
-      </c>
-      <c r="F7" t="n">
-        <v>6</v>
-      </c>
-      <c r="G7" t="n">
-        <v>349</v>
+        <v>3048.51</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>PUR-2025-022</t>
+        </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2025-12-25</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>INV-ITM-007</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>PRD-007</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>LOC-001</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>10</v>
-      </c>
-      <c r="E8" t="n">
-        <v>3</v>
-      </c>
-      <c r="F8" t="n">
-        <v>8</v>
-      </c>
-      <c r="G8" t="n">
-        <v>149</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>2025-12-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>INV-ITM-008</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>PRD-008</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>LOC-001</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>3</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>2</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1195</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>2025-12-18</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>INV-ITM-009</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>PRD-009</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>LOC-001</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>4</v>
-      </c>
-      <c r="E10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" t="n">
-        <v>3</v>
-      </c>
-      <c r="G10" t="n">
-        <v>1515</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>2025-12-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>INV-ITM-010</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>PRD-010</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>LOC-001</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>12</v>
-      </c>
-      <c r="E11" t="n">
-        <v>3</v>
-      </c>
-      <c r="F11" t="n">
-        <v>10</v>
-      </c>
-      <c r="G11" t="n">
-        <v>149</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>2025-12-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>INV-ITM-011</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>PRD-011</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>LOC-001</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>18</v>
-      </c>
-      <c r="E12" t="n">
-        <v>4</v>
-      </c>
-      <c r="F12" t="n">
-        <v>12</v>
-      </c>
-      <c r="G12" t="n">
-        <v>99</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>2025-12-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>INV-ITM-012</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>PRD-012</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>LOC-001</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>20</v>
-      </c>
-      <c r="E13" t="n">
-        <v>5</v>
-      </c>
-      <c r="F13" t="n">
-        <v>12</v>
-      </c>
-      <c r="G13" t="n">
-        <v>89</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>2025-12-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>INV-ITM-013</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>PRD-013</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>LOC-001</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>14</v>
-      </c>
-      <c r="E14" t="n">
-        <v>2</v>
-      </c>
-      <c r="F14" t="n">
-        <v>8</v>
-      </c>
-      <c r="G14" t="n">
-        <v>69</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>2025-12-22</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>INV-ITM-014</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>PRD-006</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>LOC-002</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>2</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>2</v>
-      </c>
-      <c r="G15" t="n">
-        <v>349</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>2025-12-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>INV-ITM-015</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>PRD-007</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>LOC-002</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>3</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>2</v>
-      </c>
-      <c r="G16" t="n">
-        <v>149</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>2025-12-15</t>
+          <t>DecliningBalance</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -7542,7 +7471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1">
@@ -7553,397 +7482,547 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Inventory Item ID</t>
+          <t>Product ID</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Type</t>
+          <t>Location ID</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Quantity</t>
+          <t>In Stock</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Previous Stock</t>
+          <t>Reserved</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>New Stock</t>
+          <t>Reorder Point</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Reason</t>
+          <t>Unit Cost</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Timestamp</t>
+          <t>Last Updated</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ADJ-001</t>
+          <t>INV-ITM-001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>INV-ITM-001</t>
+          <t>PRD-001</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Add</t>
+          <t>LOC-001</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>10</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Initial stock from PO-20001</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="G2" t="n">
+        <v>899</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2025-01-05 10:00:00</t>
+          <t>2025-12-28</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ADJ-002</t>
+          <t>INV-ITM-002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>INV-ITM-004</t>
+          <t>PRD-002</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Add</t>
+          <t>LOC-001</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>8</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Initial stock from PO-20002</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1349</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2025-01-12 11:00:00</t>
+          <t>2025-12-20</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ADJ-003</t>
+          <t>INV-ITM-003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>INV-ITM-006</t>
+          <t>PRD-003</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Add</t>
+          <t>LOC-001</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>10</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Initial stock from PO-20003</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="G4" t="n">
+        <v>849</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2025-01-20 09:30:00</t>
+          <t>2025-12-15</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ADJ-004</t>
+          <t>INV-ITM-004</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>INV-ITM-001</t>
+          <t>PRD-004</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remove</t>
+          <t>LOC-001</t>
         </is>
       </c>
       <c r="D5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E5" t="n">
         <v>2</v>
       </c>
-      <c r="E5" t="n">
-        <v>10</v>
-      </c>
       <c r="F5" t="n">
-        <v>8</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Sold to CUS-001</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>699</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2025-01-08 14:00:00</t>
+          <t>2025-12-28</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ADJ-005</t>
+          <t>INV-ITM-005</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>INV-ITM-004</t>
+          <t>PRD-005</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remove</t>
+          <t>LOC-001</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>5</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Sold to CUS-004</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1999</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2025-01-22 15:30:00</t>
+          <t>2025-12-22</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ADJ-006</t>
+          <t>INV-ITM-006</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>INV-ITM-001</t>
+          <t>PRD-006</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Add</t>
+          <t>LOC-001</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>16</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Restocked from PO-20011</t>
-        </is>
+        <v>6</v>
+      </c>
+      <c r="G7" t="n">
+        <v>349</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2025-07-05 10:00:00</t>
+          <t>2025-12-25</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ADJ-007</t>
+          <t>INV-ITM-007</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>INV-ITM-005</t>
+          <t>PRD-007</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Add</t>
+          <t>LOC-001</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F8" t="n">
-        <v>4</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Initial stock from PO-20007</t>
-        </is>
+        <v>8</v>
+      </c>
+      <c r="G8" t="n">
+        <v>149</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2025-04-10 11:00:00</t>
+          <t>2025-12-28</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ADJ-008</t>
+          <t>INV-ITM-008</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>INV-ITM-002</t>
+          <t>PRD-008</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Add</t>
+          <t>LOC-001</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>5</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Initial stock from PO-20009</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1195</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2025-05-08 09:00:00</t>
+          <t>2025-12-18</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ADJ-009</t>
+          <t>INV-ITM-009</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>INV-ITM-013</t>
+          <t>PRD-009</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remove</t>
+          <t>LOC-001</t>
         </is>
       </c>
       <c r="D10" t="n">
+        <v>4</v>
+      </c>
+      <c r="E10" t="n">
         <v>1</v>
       </c>
-      <c r="E10" t="n">
-        <v>15</v>
-      </c>
       <c r="F10" t="n">
-        <v>14</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Damaged during handling</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1515</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2025-08-15 16:00:00</t>
+          <t>2025-12-10</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ADJ-010</t>
+          <t>INV-ITM-010</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>INV-ITM-001</t>
+          <t>PRD-010</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Add</t>
+          <t>LOC-001</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" t="n">
         <v>10</v>
       </c>
-      <c r="F11" t="n">
-        <v>16</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Restocked from PO-20014</t>
-        </is>
+      <c r="G11" t="n">
+        <v>149</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2025-10-05 10:30:00</t>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>INV-ITM-011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>PRD-011</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>LOC-001</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>18</v>
+      </c>
+      <c r="E12" t="n">
+        <v>4</v>
+      </c>
+      <c r="F12" t="n">
+        <v>12</v>
+      </c>
+      <c r="G12" t="n">
+        <v>99</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>INV-ITM-012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>PRD-012</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>LOC-001</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>20</v>
+      </c>
+      <c r="E13" t="n">
+        <v>5</v>
+      </c>
+      <c r="F13" t="n">
+        <v>12</v>
+      </c>
+      <c r="G13" t="n">
+        <v>89</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>INV-ITM-013</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>PRD-013</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>LOC-001</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>14</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" t="n">
+        <v>8</v>
+      </c>
+      <c r="G14" t="n">
+        <v>69</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>INV-ITM-014</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>PRD-006</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>LOC-002</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" t="n">
+        <v>349</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>INV-ITM-015</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>PRD-007</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>LOC-002</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>3</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" t="n">
+        <v>149</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
         </is>
       </c>
     </row>
@@ -7958,7 +8037,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1">
@@ -7969,267 +8048,397 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Supplier ID</t>
+          <t>Inventory Item ID</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Order Date</t>
+          <t>Type</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Expected Date</t>
+          <t>Quantity</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Previous Stock</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>New Stock</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Reason</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Timestamp</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PO-001</t>
+          <t>ADJ-001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SUP-001</t>
+          <t>INV-ITM-001</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2025-01-02</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2025-01-09</t>
-        </is>
+          <t>Add</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>10</v>
       </c>
       <c r="E2" t="n">
-        <v>9731.68</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Received</t>
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Initial stock from PO-20001</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2025-01-05 10:00:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PO-002</t>
+          <t>ADJ-002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SUP-001</t>
+          <t>INV-ITM-004</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2025-01-17</t>
-        </is>
+          <t>Add</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>6053.34</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Received</t>
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>8</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Initial stock from PO-20002</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2025-01-12 11:00:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PO-003</t>
+          <t>ADJ-003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SUP-004</t>
+          <t>INV-ITM-006</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2025-02-12</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2025-02-19</t>
-        </is>
+          <t>Add</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>10</v>
       </c>
       <c r="E4" t="n">
-        <v>3880.76</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Received</t>
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Initial stock from PO-20003</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2025-01-20 09:30:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PO-004</t>
+          <t>ADJ-004</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SUP-001</t>
+          <t>INV-ITM-001</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2025-04-15</t>
-        </is>
+          <t>Remove</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>8655.67</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Received</t>
+        <v>10</v>
+      </c>
+      <c r="F5" t="n">
+        <v>8</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Sold to CUS-001</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2025-01-08 14:00:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PO-005</t>
+          <t>ADJ-005</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SUP-001</t>
+          <t>INV-ITM-004</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2025-07-09</t>
-        </is>
+          <t>Remove</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>7785.34</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Received</t>
+        <v>8</v>
+      </c>
+      <c r="F6" t="n">
+        <v>5</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Sold to CUS-004</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2025-01-22 15:30:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PO-006</t>
+          <t>ADJ-006</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SUP-001</t>
+          <t>INV-ITM-001</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2025-10-09</t>
-        </is>
+          <t>Add</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>5839.01</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Received</t>
+        <v>8</v>
+      </c>
+      <c r="F7" t="n">
+        <v>16</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Restocked from PO-20011</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2025-07-05 10:00:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PO-007</t>
+          <t>ADJ-007</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SUP-001</t>
+          <t>INV-ITM-005</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2025-12-27</t>
-        </is>
+          <t>Add</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>4</v>
       </c>
       <c r="E8" t="n">
-        <v>6491.75</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Sent</t>
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>4</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Initial stock from PO-20007</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2025-04-10 11:00:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PO-008</t>
+          <t>ADJ-008</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SUP-007</t>
+          <t>INV-ITM-002</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2026-01-05</t>
-        </is>
+          <t>Add</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>5</v>
       </c>
       <c r="E9" t="n">
-        <v>5514.26</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Draft</t>
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>5</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Initial stock from PO-20009</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2025-05-08 09:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ADJ-009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>INV-ITM-013</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Remove</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>15</v>
+      </c>
+      <c r="F10" t="n">
+        <v>14</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Damaged during handling</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2025-08-15 16:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ADJ-010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>INV-ITM-001</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Add</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>6</v>
+      </c>
+      <c r="E11" t="n">
+        <v>10</v>
+      </c>
+      <c r="F11" t="n">
+        <v>16</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Restocked from PO-20014</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2025-10-05 10:30:00</t>
         </is>
       </c>
     </row>
@@ -8244,7 +8453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1">
@@ -8255,267 +8464,267 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Supplier ID</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Total Qty</t>
+          <t>Order Date</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Available</t>
+          <t>Expected Date</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Rented</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Daily Rate</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Weekly Rate</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Monthly Rate</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Deposit</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
           <t>Status</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Product ID</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>RNT-ITM-001</t>
+          <t>PO-001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>HD Projector</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>4</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3</v>
+          <t>SUP-001</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2025-01-02</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2025-01-09</t>
+        </is>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" t="n">
-        <v>75</v>
-      </c>
-      <c r="G2" t="n">
-        <v>300</v>
-      </c>
-      <c r="H2" t="n">
-        <v>800</v>
-      </c>
-      <c r="I2" t="n">
-        <v>250</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>PRD-041</t>
+        <v>9731.68</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Received</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>RNT-ITM-002</t>
+          <t>PO-002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Conference Room AV Kit</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D3" t="n">
-        <v>1</v>
+          <t>SUP-001</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2025-01-17</t>
+        </is>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" t="n">
-        <v>150</v>
-      </c>
-      <c r="G3" t="n">
-        <v>600</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1800</v>
-      </c>
-      <c r="I3" t="n">
-        <v>500</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>PRD-042</t>
+        <v>6053.34</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Received</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>RNT-ITM-003</t>
+          <t>PO-003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Laptop Rental Unit</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>7</v>
+          <t>SUP-004</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2025-02-12</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2025-02-19</t>
+        </is>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
-      </c>
-      <c r="F4" t="n">
-        <v>50</v>
-      </c>
-      <c r="G4" t="n">
-        <v>200</v>
-      </c>
-      <c r="H4" t="n">
-        <v>600</v>
-      </c>
-      <c r="I4" t="n">
-        <v>300</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>PRD-043</t>
+        <v>3880.76</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Received</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>RNT-ITM-004</t>
+          <t>PO-004</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Portable PA System</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D5" t="n">
-        <v>2</v>
+          <t>SUP-001</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" t="n">
-        <v>100</v>
-      </c>
-      <c r="G5" t="n">
-        <v>400</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1200</v>
-      </c>
-      <c r="I5" t="n">
-        <v>400</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>PRD-044</t>
+        <v>8655.67</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Received</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>RNT-ITM-005</t>
+          <t>PO-005</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Display Monitor (Large)</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>6</v>
-      </c>
-      <c r="D6" t="n">
-        <v>4</v>
+          <t>SUP-001</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F6" t="n">
-        <v>40</v>
-      </c>
-      <c r="G6" t="n">
-        <v>160</v>
-      </c>
-      <c r="H6" t="n">
-        <v>500</v>
-      </c>
-      <c r="I6" t="n">
-        <v>200</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>PRD-045</t>
+        <v>7785.34</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PO-006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SUP-001</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5839.01</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>PO-007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>SUP-001</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2025-12-27</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6491.75</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>PO-008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>SUP-007</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5514.26</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Draft</t>
         </is>
       </c>
     </row>
@@ -8530,7 +8739,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1">
@@ -8541,524 +8750,267 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Customer ID</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rental Item ID</t>
+          <t>Total Qty</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Quantity</t>
+          <t>Available</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Rate Type</t>
+          <t>Rented</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Rate Amount</t>
+          <t>Daily Rate</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Security Deposit</t>
+          <t>Weekly Rate</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Start Date</t>
+          <t>Monthly Rate</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Due Date</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Return Date</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Total Cost</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Paid</t>
+          <t>Product ID</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>RNT-001</t>
+          <t>RNT-ITM-001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CUS-003</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>RNT-ITM-001</t>
-        </is>
+          <t>HD Projector</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>4</v>
       </c>
       <c r="D2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2" t="n">
         <v>1</v>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Weekly</t>
-        </is>
-      </c>
       <c r="F2" t="n">
+        <v>75</v>
+      </c>
+      <c r="G2" t="n">
         <v>300</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
+        <v>800</v>
+      </c>
+      <c r="I2" t="n">
         <v>250</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>2025-03-10</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2025-03-17</t>
-        </is>
-      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>300</v>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Returned</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>PRD-041</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>RNT-002</t>
+          <t>RNT-ITM-002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CUS-009</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>RNT-ITM-002</t>
-        </is>
+          <t>Conference Room AV Kit</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
       </c>
       <c r="D3" t="n">
         <v>1</v>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Weekly</t>
-        </is>
+      <c r="E3" t="n">
+        <v>1</v>
       </c>
       <c r="F3" t="n">
+        <v>150</v>
+      </c>
+      <c r="G3" t="n">
         <v>600</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="I3" t="n">
         <v>500</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>2025-05-05</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2025-05-12</t>
-        </is>
-      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>600</v>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Returned</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>PRD-042</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>RNT-003</t>
+          <t>RNT-ITM-003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CUS-007</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>RNT-ITM-003</t>
-        </is>
+          <t>Laptop Rental Unit</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
       </c>
       <c r="D4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E4" t="n">
         <v>3</v>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Weekly</t>
-        </is>
-      </c>
       <c r="F4" t="n">
+        <v>50</v>
+      </c>
+      <c r="G4" t="n">
         <v>200</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
+        <v>600</v>
+      </c>
+      <c r="I4" t="n">
         <v>300</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>2025-07-15</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2025-07-22</t>
-        </is>
-      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>600</v>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Returned</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>PRD-043</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>RNT-004</t>
+          <t>RNT-ITM-004</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CUS-011</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>RNT-ITM-001</t>
-        </is>
+          <t>Portable PA System</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
       </c>
       <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="n">
         <v>1</v>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Weekly</t>
-        </is>
-      </c>
       <c r="F5" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="G5" t="n">
-        <v>250</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2025-09-27</t>
-        </is>
+        <v>400</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1200</v>
+      </c>
+      <c r="I5" t="n">
+        <v>400</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>300</v>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Returned</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>PRD-044</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>RNT-005</t>
+          <t>RNT-ITM-005</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CUS-015</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>RNT-ITM-004</t>
-        </is>
+          <t>Display Monitor (Large)</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Weekly</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>400</v>
+        <v>40</v>
       </c>
       <c r="G6" t="n">
-        <v>400</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2025-10-17</t>
-        </is>
+        <v>160</v>
+      </c>
+      <c r="H6" t="n">
+        <v>500</v>
+      </c>
+      <c r="I6" t="n">
+        <v>200</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>400</v>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>Returned</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>RNT-006</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>CUS-003</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>RNT-ITM-005</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Weekly</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>160</v>
-      </c>
-      <c r="G7" t="n">
-        <v>200</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>2025-12-15</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2025-12-22</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>2025-12-22</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>320</v>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>Returned</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>RNT-007</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>CUS-011</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>RNT-ITM-001</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Weekly</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>300</v>
-      </c>
-      <c r="G8" t="n">
-        <v>250</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>2025-12-26</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2026-01-02</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>300</v>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>RNT-008</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>CUS-009</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>RNT-ITM-003</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Weekly</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>200</v>
-      </c>
-      <c r="G9" t="n">
-        <v>300</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>2025-12-28</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2026-01-04</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>400</v>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>PRD-045</t>
         </is>
       </c>
     </row>
@@ -9073,7 +9025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1">
@@ -9089,167 +9041,519 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Amount</t>
+          <t>Rental Item ID</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Quantity</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Frequency</t>
+          <t>Rate Type</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Next Date</t>
+          <t>Rate Amount</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>Security Deposit</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Start Date</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Due Date</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Return Date</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Total Cost</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t>Status</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Paid</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>REC-INV-001</t>
+          <t>RNT-001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CUS-002</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>800</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Monthly IT Support Contract</t>
-        </is>
+          <t>CUS-003</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>RNT-ITM-001</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Monthly</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>2026-01-02</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Active</t>
+          <t>Weekly</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>300</v>
+      </c>
+      <c r="G2" t="n">
+        <v>250</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2025-03-17</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>2025-03-17</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>300</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Returned</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>REC-INV-002</t>
+          <t>RNT-002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CUS-001</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>528</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>CloudOffice Business Premium (2 users)</t>
-        </is>
+          <t>CUS-009</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>RNT-ITM-002</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Monthly</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2026-01-15</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Active</t>
+          <t>Weekly</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>600</v>
+      </c>
+      <c r="G3" t="n">
+        <v>500</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>600</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Returned</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>REC-INV-003</t>
+          <t>RNT-003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CUS-006</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>1200</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Quarterly Network Maintenance</t>
-        </is>
+          <t>CUS-007</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>RNT-ITM-003</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2026-01-25</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Active</t>
+          <t>Weekly</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>200</v>
+      </c>
+      <c r="G4" t="n">
+        <v>300</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>600</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Returned</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>REC-INV-004</t>
+          <t>RNT-004</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CUS-012</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>2400</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Annual Support Agreement</t>
-        </is>
+          <t>CUS-011</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>RNT-ITM-001</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Annually</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+          <t>Weekly</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>300</v>
+      </c>
+      <c r="G5" t="n">
+        <v>250</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>300</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Returned</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>RNT-005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CUS-015</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>RNT-ITM-004</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>400</v>
+      </c>
+      <c r="G6" t="n">
+        <v>400</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>400</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Returned</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>RNT-006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CUS-003</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>RNT-ITM-005</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>160</v>
+      </c>
+      <c r="G7" t="n">
+        <v>200</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>320</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Returned</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>RNT-007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>CUS-011</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>RNT-ITM-001</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G8" t="n">
+        <v>250</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-01-02</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>300</v>
+      </c>
+      <c r="L8" t="inlineStr">
         <is>
           <t>Active</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>RNT-008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>CUS-009</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>RNT-ITM-003</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>200</v>
+      </c>
+      <c r="G9" t="n">
+        <v>300</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-01-04</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>400</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9259,6 +9563,197 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Customer ID</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Frequency</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Next Date</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>REC-INV-001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>CUS-002</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>800</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Monthly IT Support Contract</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-01-02</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>REC-INV-002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CUS-001</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>528</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>CloudOffice Business Premium (2 users)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>REC-INV-003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>CUS-006</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Quarterly Network Maintenance</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>REC-INV-004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>CUS-012</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>2400</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Annual Support Agreement</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Annually</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9726,332 +10221,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Original Transaction ID</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Return Type</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Customer ID</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Supplier ID</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Quantity</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Return Date</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Refund Amount</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Restocking Fee</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Reason</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>RET-001</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>PUR-2025-005</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>SUP-004</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>SecureGate MX68 Firewall</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>46025.88398792824</v>
-      </c>
-      <c r="I2" t="n">
-        <v>411.1</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Defective</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>RET-002</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>PUR-2025-008</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>SUP-004</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>NetSwitch 1000-24T</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>46035.88398792824</v>
-      </c>
-      <c r="I3" t="n">
-        <v>170.61</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Not as described</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>RET-003</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>PUR-2025-010</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>SUP-002</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>PeripheralPro Bundle</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>46045.88398792824</v>
-      </c>
-      <c r="I4" t="n">
-        <v>89.98999999999999</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Changed mind</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>RET-004</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>SAL-2025-013</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Customer</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>CUS-006</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>ByteForge ThinkPad T14</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>46030.88398792824</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1299</v>
-      </c>
-      <c r="J5" t="n">
-        <v>50</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Defective</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>RET-005</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>SAL-2025-006</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Customer</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>CUS-004</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>WorkStation 7010 Desktop</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>46040.88398792824</v>
-      </c>
-      <c r="I6" t="n">
-        <v>899</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Changed mind</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -10585,6 +10754,332 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Original Transaction ID</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Return Type</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Customer ID</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Supplier ID</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Return Date</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Refund Amount</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Restocking Fee</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Reason</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>RET-001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>PUR-2025-005</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>SUP-004</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SecureGate MX68 Firewall</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>46025.88398792824</v>
+      </c>
+      <c r="I2" t="n">
+        <v>411.1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Defective</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>RET-002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>PUR-2025-008</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>SUP-004</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>NetSwitch 1000-24T</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>46035.88398792824</v>
+      </c>
+      <c r="I3" t="n">
+        <v>170.61</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Not as described</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>RET-003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>PUR-2025-010</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>SUP-002</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>PeripheralPro Bundle</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>46045.88398792824</v>
+      </c>
+      <c r="I4" t="n">
+        <v>89.98999999999999</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Changed mind</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>RET-004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SAL-2025-013</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Customer</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>CUS-006</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>ByteForge ThinkPad T14</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>46030.88398792824</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1299</v>
+      </c>
+      <c r="J5" t="n">
+        <v>50</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Defective</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>RET-005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>SAL-2025-006</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Customer</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>CUS-004</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>WorkStation 7010 Desktop</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>46040.88398792824</v>
+      </c>
+      <c r="I6" t="n">
+        <v>899</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Changed mind</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <sheetData>
@@ -10769,7 +11264,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1">
@@ -11346,6 +11841,33 @@
         </is>
       </c>
       <c r="F17" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>CAT-PUR-006</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Equipment and Vehicles</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Vehicles, furniture and equipment kept for years</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
         <is>
           <t>Product</t>
         </is>
@@ -11362,7 +11884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L46"/>
+  <dimension ref="A1:L49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="8.7265625" customWidth="1" min="2" max="2"/>
@@ -13908,6 +14430,132 @@
       </c>
       <c r="L46" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>PRD-046</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Delivery Van</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>EXP-VAN</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Cargo van for customer deliveries</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>CAT-PUR-006</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Equipment and Vehicles</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>PRD-047</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Staff Laptops</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>EXP-STAFF-LAPTOPS</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Laptops for staff to use, not for resale</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>CAT-PUR-006</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Equipment and Vehicles</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>PRD-048</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Label Printer</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>EXP-LABEL-PRINTER</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Thermal label printer for shipping</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>CAT-PUR-006</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Equipment and Vehicles</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/ArgoBooks/Resources/SampleCompanyData.xlsx
+++ b/ArgoBooks/Resources/SampleCompanyData.xlsx
@@ -7019,13 +7019,13 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>32000</v>
+        <v>7500</v>
       </c>
       <c r="F38" t="n">
-        <v>1600</v>
+        <v>375</v>
       </c>
       <c r="G38" t="n">
-        <v>33600</v>
+        <v>7875</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -7288,7 +7288,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Delivery van</t>
+          <t>Used delivery van</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -7302,7 +7302,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>32000</v>
+        <v>7500</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -14460,7 +14460,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Cargo van for customer deliveries</t>
+          <t>Used cargo van for customer deliveries</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">

--- a/ArgoBooks/Resources/SampleCompanyData.xlsx
+++ b/ArgoBooks/Resources/SampleCompanyData.xlsx
@@ -1575,10 +1575,10 @@
         <v>1189.03</v>
       </c>
       <c r="F2" t="n">
-        <v>98.09999999999999</v>
+        <v>154.57</v>
       </c>
       <c r="G2" t="n">
-        <v>1287.12</v>
+        <v>1343.6</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -1619,10 +1619,10 @@
         <v>1189.03</v>
       </c>
       <c r="F3" t="n">
-        <v>98.09999999999999</v>
+        <v>154.57</v>
       </c>
       <c r="G3" t="n">
-        <v>1287.12</v>
+        <v>1343.6</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -1663,10 +1663,10 @@
         <v>1189.03</v>
       </c>
       <c r="F4" t="n">
-        <v>98.09999999999999</v>
+        <v>154.57</v>
       </c>
       <c r="G4" t="n">
-        <v>1287.12</v>
+        <v>1343.6</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -1704,10 +1704,10 @@
         <v>502.52</v>
       </c>
       <c r="F5" t="n">
-        <v>41.46</v>
+        <v>65.33</v>
       </c>
       <c r="G5" t="n">
-        <v>543.98</v>
+        <v>567.85</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -1748,10 +1748,10 @@
         <v>502.52</v>
       </c>
       <c r="F6" t="n">
-        <v>41.46</v>
+        <v>65.33</v>
       </c>
       <c r="G6" t="n">
-        <v>543.98</v>
+        <v>567.85</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -1789,10 +1789,10 @@
         <v>822.89</v>
       </c>
       <c r="F7" t="n">
-        <v>67.89</v>
+        <v>106.98</v>
       </c>
       <c r="G7" t="n">
-        <v>890.78</v>
+        <v>929.87</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1830,10 +1830,10 @@
         <v>822.89</v>
       </c>
       <c r="F8" t="n">
-        <v>67.89</v>
+        <v>106.98</v>
       </c>
       <c r="G8" t="n">
-        <v>890.78</v>
+        <v>929.87</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1871,10 +1871,10 @@
         <v>822.89</v>
       </c>
       <c r="F9" t="n">
-        <v>67.89</v>
+        <v>106.98</v>
       </c>
       <c r="G9" t="n">
-        <v>890.78</v>
+        <v>929.87</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1915,10 +1915,10 @@
         <v>822.89</v>
       </c>
       <c r="F10" t="n">
-        <v>67.89</v>
+        <v>106.98</v>
       </c>
       <c r="G10" t="n">
-        <v>890.78</v>
+        <v>929.87</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1959,10 +1959,10 @@
         <v>227.92</v>
       </c>
       <c r="F11" t="n">
-        <v>18.8</v>
+        <v>29.63</v>
       </c>
       <c r="G11" t="n">
-        <v>246.72</v>
+        <v>257.55</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -2003,10 +2003,10 @@
         <v>227.92</v>
       </c>
       <c r="F12" t="n">
-        <v>18.8</v>
+        <v>29.63</v>
       </c>
       <c r="G12" t="n">
-        <v>246.72</v>
+        <v>257.55</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -2047,10 +2047,10 @@
         <v>1291.7</v>
       </c>
       <c r="F13" t="n">
-        <v>106.57</v>
+        <v>167.92</v>
       </c>
       <c r="G13" t="n">
-        <v>1398.27</v>
+        <v>1459.62</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -2091,10 +2091,10 @@
         <v>1236.8</v>
       </c>
       <c r="F14" t="n">
-        <v>102.03</v>
+        <v>160.78</v>
       </c>
       <c r="G14" t="n">
-        <v>1338.84</v>
+        <v>1397.58</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -2135,10 +2135,10 @@
         <v>1236.8</v>
       </c>
       <c r="F15" t="n">
-        <v>102.03</v>
+        <v>160.78</v>
       </c>
       <c r="G15" t="n">
-        <v>1338.84</v>
+        <v>1397.58</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -2179,10 +2179,10 @@
         <v>1236.8</v>
       </c>
       <c r="F16" t="n">
-        <v>102.03</v>
+        <v>160.78</v>
       </c>
       <c r="G16" t="n">
-        <v>1338.84</v>
+        <v>1397.58</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -2223,10 +2223,10 @@
         <v>2039.81</v>
       </c>
       <c r="F17" t="n">
-        <v>168.29</v>
+        <v>265.18</v>
       </c>
       <c r="G17" t="n">
-        <v>2208.1</v>
+        <v>2304.99</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -2264,10 +2264,10 @@
         <v>1215.14</v>
       </c>
       <c r="F18" t="n">
-        <v>100.25</v>
+        <v>157.97</v>
       </c>
       <c r="G18" t="n">
-        <v>1315.39</v>
+        <v>1373.11</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -2308,10 +2308,10 @@
         <v>1315.39</v>
       </c>
       <c r="F19" t="n">
-        <v>108.52</v>
+        <v>171</v>
       </c>
       <c r="G19" t="n">
-        <v>1423.91</v>
+        <v>1486.39</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -2349,10 +2349,10 @@
         <v>1315.39</v>
       </c>
       <c r="F20" t="n">
-        <v>108.52</v>
+        <v>171</v>
       </c>
       <c r="G20" t="n">
-        <v>1423.91</v>
+        <v>1486.39</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -2390,10 +2390,10 @@
         <v>252.14</v>
       </c>
       <c r="F21" t="n">
-        <v>20.8</v>
+        <v>32.78</v>
       </c>
       <c r="G21" t="n">
-        <v>272.94</v>
+        <v>284.92</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -2434,10 +2434,10 @@
         <v>910.34</v>
       </c>
       <c r="F22" t="n">
-        <v>75.11</v>
+        <v>118.34</v>
       </c>
       <c r="G22" t="n">
-        <v>985.45</v>
+        <v>1028.68</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -2475,10 +2475,10 @@
         <v>910.34</v>
       </c>
       <c r="F23" t="n">
-        <v>75.11</v>
+        <v>118.34</v>
       </c>
       <c r="G23" t="n">
-        <v>985.45</v>
+        <v>1028.68</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -2519,10 +2519,10 @@
         <v>252.14</v>
       </c>
       <c r="F24" t="n">
-        <v>20.8</v>
+        <v>32.78</v>
       </c>
       <c r="G24" t="n">
-        <v>272.94</v>
+        <v>284.92</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -2563,10 +2563,10 @@
         <v>1327.5</v>
       </c>
       <c r="F25" t="n">
-        <v>109.52</v>
+        <v>172.58</v>
       </c>
       <c r="G25" t="n">
-        <v>1437.02</v>
+        <v>1500.08</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -2607,10 +2607,10 @@
         <v>3207.03</v>
       </c>
       <c r="F26" t="n">
-        <v>264.58</v>
+        <v>416.91</v>
       </c>
       <c r="G26" t="n">
-        <v>3471.61</v>
+        <v>3623.94</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -2651,10 +2651,10 @@
         <v>3207.03</v>
       </c>
       <c r="F27" t="n">
-        <v>264.58</v>
+        <v>416.91</v>
       </c>
       <c r="G27" t="n">
-        <v>3471.61</v>
+        <v>3623.94</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -2692,10 +2692,10 @@
         <v>607.33</v>
       </c>
       <c r="F28" t="n">
-        <v>50.1</v>
+        <v>78.95</v>
       </c>
       <c r="G28" t="n">
-        <v>657.4299999999999</v>
+        <v>686.28</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -2736,10 +2736,10 @@
         <v>607.33</v>
       </c>
       <c r="F29" t="n">
-        <v>50.1</v>
+        <v>78.95</v>
       </c>
       <c r="G29" t="n">
-        <v>657.4299999999999</v>
+        <v>686.28</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -2777,10 +2777,10 @@
         <v>1437.02</v>
       </c>
       <c r="F30" t="n">
-        <v>118.56</v>
+        <v>186.81</v>
       </c>
       <c r="G30" t="n">
-        <v>1555.58</v>
+        <v>1623.83</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -2821,10 +2821,10 @@
         <v>1437.02</v>
       </c>
       <c r="F31" t="n">
-        <v>118.56</v>
+        <v>186.81</v>
       </c>
       <c r="G31" t="n">
-        <v>1555.58</v>
+        <v>1623.83</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -2865,10 +2865,10 @@
         <v>1119.22</v>
       </c>
       <c r="F32" t="n">
-        <v>92.34</v>
+        <v>145.5</v>
       </c>
       <c r="G32" t="n">
-        <v>1211.56</v>
+        <v>1264.72</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -2909,10 +2909,10 @@
         <v>1771.17</v>
       </c>
       <c r="F33" t="n">
-        <v>146.12</v>
+        <v>230.25</v>
       </c>
       <c r="G33" t="n">
-        <v>1917.3</v>
+        <v>2001.42</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -2953,10 +2953,10 @@
         <v>1771.17</v>
       </c>
       <c r="F34" t="n">
-        <v>146.12</v>
+        <v>230.25</v>
       </c>
       <c r="G34" t="n">
-        <v>1917.3</v>
+        <v>2001.42</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -2994,10 +2994,10 @@
         <v>1771.17</v>
       </c>
       <c r="F35" t="n">
-        <v>146.12</v>
+        <v>230.25</v>
       </c>
       <c r="G35" t="n">
-        <v>1917.3</v>
+        <v>2001.42</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -3038,10 +3038,10 @@
         <v>2047.25</v>
       </c>
       <c r="F36" t="n">
-        <v>168.9</v>
+        <v>266.14</v>
       </c>
       <c r="G36" t="n">
-        <v>2216.15</v>
+        <v>2313.39</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -3082,10 +3082,10 @@
         <v>890.8200000000001</v>
       </c>
       <c r="F37" t="n">
-        <v>73.48999999999999</v>
+        <v>115.81</v>
       </c>
       <c r="G37" t="n">
-        <v>964.3200000000001</v>
+        <v>1006.63</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -3123,10 +3123,10 @@
         <v>2152.08</v>
       </c>
       <c r="F38" t="n">
-        <v>177.55</v>
+        <v>279.77</v>
       </c>
       <c r="G38" t="n">
-        <v>2329.63</v>
+        <v>2431.85</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -3164,10 +3164,10 @@
         <v>2152.08</v>
       </c>
       <c r="F39" t="n">
-        <v>177.55</v>
+        <v>279.77</v>
       </c>
       <c r="G39" t="n">
-        <v>2329.63</v>
+        <v>2431.85</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -3208,10 +3208,10 @@
         <v>407.55</v>
       </c>
       <c r="F40" t="n">
-        <v>33.62</v>
+        <v>52.98</v>
       </c>
       <c r="G40" t="n">
-        <v>441.17</v>
+        <v>460.53</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -3249,10 +3249,10 @@
         <v>2598.24</v>
       </c>
       <c r="F41" t="n">
-        <v>214.35</v>
+        <v>337.77</v>
       </c>
       <c r="G41" t="n">
-        <v>2812.59</v>
+        <v>2936.01</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -3290,10 +3290,10 @@
         <v>3117.89</v>
       </c>
       <c r="F42" t="n">
-        <v>257.23</v>
+        <v>405.33</v>
       </c>
       <c r="G42" t="n">
-        <v>3375.11</v>
+        <v>3523.22</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -3331,10 +3331,10 @@
         <v>1539.88</v>
       </c>
       <c r="F43" t="n">
-        <v>127.04</v>
+        <v>200.18</v>
       </c>
       <c r="G43" t="n">
-        <v>1666.92</v>
+        <v>1740.06</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -3375,10 +3375,10 @@
         <v>1666.92</v>
       </c>
       <c r="F44" t="n">
-        <v>137.52</v>
+        <v>216.7</v>
       </c>
       <c r="G44" t="n">
-        <v>1804.44</v>
+        <v>1883.62</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -3416,10 +3416,10 @@
         <v>1666.92</v>
       </c>
       <c r="F45" t="n">
-        <v>137.52</v>
+        <v>216.7</v>
       </c>
       <c r="G45" t="n">
-        <v>1804.44</v>
+        <v>1883.62</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -3457,10 +3457,10 @@
         <v>319.52</v>
       </c>
       <c r="F46" t="n">
-        <v>26.36</v>
+        <v>41.54</v>
       </c>
       <c r="G46" t="n">
-        <v>345.88</v>
+        <v>361.06</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         <v>5389.57</v>
       </c>
       <c r="F47" t="n">
-        <v>444.64</v>
+        <v>700.64</v>
       </c>
       <c r="G47" t="n">
-        <v>5834.21</v>
+        <v>6090.21</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -3539,10 +3539,10 @@
         <v>1152.76</v>
       </c>
       <c r="F48" t="n">
-        <v>95.09999999999999</v>
+        <v>149.86</v>
       </c>
       <c r="G48" t="n">
-        <v>1247.86</v>
+        <v>1302.62</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -3583,10 +3583,10 @@
         <v>1247.86</v>
       </c>
       <c r="F49" t="n">
-        <v>102.95</v>
+        <v>162.22</v>
       </c>
       <c r="G49" t="n">
-        <v>1350.81</v>
+        <v>1410.08</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -3624,10 +3624,10 @@
         <v>239.2</v>
       </c>
       <c r="F50" t="n">
-        <v>19.73</v>
+        <v>31.1</v>
       </c>
       <c r="G50" t="n">
-        <v>258.93</v>
+        <v>270.3</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -3668,10 +3668,10 @@
         <v>1820.39</v>
       </c>
       <c r="F51" t="n">
-        <v>150.18</v>
+        <v>236.65</v>
       </c>
       <c r="G51" t="n">
-        <v>1970.58</v>
+        <v>2057.04</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -3712,10 +3712,10 @@
         <v>1414.15</v>
       </c>
       <c r="F52" t="n">
-        <v>116.67</v>
+        <v>183.84</v>
       </c>
       <c r="G52" t="n">
-        <v>1530.82</v>
+        <v>1597.99</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -3756,10 +3756,10 @@
         <v>1059.43</v>
       </c>
       <c r="F53" t="n">
-        <v>87.41</v>
+        <v>137.73</v>
       </c>
       <c r="G53" t="n">
-        <v>1146.84</v>
+        <v>1197.16</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -3800,10 +3800,10 @@
         <v>1059.43</v>
       </c>
       <c r="F54" t="n">
-        <v>87.41</v>
+        <v>137.73</v>
       </c>
       <c r="G54" t="n">
-        <v>1146.84</v>
+        <v>1197.16</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -3844,10 +3844,10 @@
         <v>622.23</v>
       </c>
       <c r="F55" t="n">
-        <v>51.33</v>
+        <v>80.89</v>
       </c>
       <c r="G55" t="n">
-        <v>673.5599999999999</v>
+        <v>703.12</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -3888,10 +3888,10 @@
         <v>622.23</v>
       </c>
       <c r="F56" t="n">
-        <v>51.33</v>
+        <v>80.89</v>
       </c>
       <c r="G56" t="n">
-        <v>673.5599999999999</v>
+        <v>703.12</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -3932,10 +3932,10 @@
         <v>2403.32</v>
       </c>
       <c r="F57" t="n">
-        <v>198.27</v>
+        <v>312.43</v>
       </c>
       <c r="G57" t="n">
-        <v>2601.59</v>
+        <v>2715.75</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -3973,10 +3973,10 @@
         <v>2601.59</v>
       </c>
       <c r="F58" t="n">
-        <v>214.64</v>
+        <v>338.21</v>
       </c>
       <c r="G58" t="n">
-        <v>2816.23</v>
+        <v>2939.8</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -4014,10 +4014,10 @@
         <v>2601.59</v>
       </c>
       <c r="F59" t="n">
-        <v>214.64</v>
+        <v>338.21</v>
       </c>
       <c r="G59" t="n">
-        <v>2816.23</v>
+        <v>2939.8</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -4058,10 +4058,10 @@
         <v>498.69</v>
       </c>
       <c r="F60" t="n">
-        <v>41.14</v>
+        <v>64.83</v>
       </c>
       <c r="G60" t="n">
-        <v>539.83</v>
+        <v>563.52</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -4099,10 +4099,10 @@
         <v>1399.93</v>
       </c>
       <c r="F61" t="n">
-        <v>115.5</v>
+        <v>181.99</v>
       </c>
       <c r="G61" t="n">
-        <v>1515.43</v>
+        <v>1581.92</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -4140,10 +4140,10 @@
         <v>1399.93</v>
       </c>
       <c r="F62" t="n">
-        <v>115.5</v>
+        <v>181.99</v>
       </c>
       <c r="G62" t="n">
-        <v>1515.43</v>
+        <v>1581.92</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -4184,10 +4184,10 @@
         <v>1242.3</v>
       </c>
       <c r="F63" t="n">
-        <v>102.49</v>
+        <v>161.5</v>
       </c>
       <c r="G63" t="n">
-        <v>1344.79</v>
+        <v>1403.8</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -4225,10 +4225,10 @@
         <v>930.6900000000001</v>
       </c>
       <c r="F64" t="n">
-        <v>76.78</v>
+        <v>120.99</v>
       </c>
       <c r="G64" t="n">
-        <v>1007.48</v>
+        <v>1051.68</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -4269,10 +4269,10 @@
         <v>930.6900000000001</v>
       </c>
       <c r="F65" t="n">
-        <v>76.78</v>
+        <v>120.99</v>
       </c>
       <c r="G65" t="n">
-        <v>1007.48</v>
+        <v>1051.68</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -4313,10 +4313,10 @@
         <v>257.78</v>
       </c>
       <c r="F66" t="n">
-        <v>21.26</v>
+        <v>33.51</v>
       </c>
       <c r="G66" t="n">
-        <v>279.04</v>
+        <v>291.29</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -4357,10 +4357,10 @@
         <v>5693.9</v>
       </c>
       <c r="F67" t="n">
-        <v>469.75</v>
+        <v>740.21</v>
       </c>
       <c r="G67" t="n">
-        <v>6163.64</v>
+        <v>6434.11</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -4398,10 +4398,10 @@
         <v>976.46</v>
       </c>
       <c r="F68" t="n">
-        <v>80.56</v>
+        <v>126.94</v>
       </c>
       <c r="G68" t="n">
-        <v>1057.02</v>
+        <v>1103.4</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -4442,10 +4442,10 @@
         <v>1545.25</v>
       </c>
       <c r="F69" t="n">
-        <v>127.49</v>
+        <v>200.88</v>
       </c>
       <c r="G69" t="n">
-        <v>1672.74</v>
+        <v>1746.13</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -4483,10 +4483,10 @@
         <v>1545.25</v>
       </c>
       <c r="F70" t="n">
-        <v>127.49</v>
+        <v>200.88</v>
       </c>
       <c r="G70" t="n">
-        <v>1672.74</v>
+        <v>1746.13</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -4527,10 +4527,10 @@
         <v>2848.01</v>
       </c>
       <c r="F71" t="n">
-        <v>234.96</v>
+        <v>370.24</v>
       </c>
       <c r="G71" t="n">
-        <v>3082.98</v>
+        <v>3218.25</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -4568,10 +4568,10 @@
         <v>2358.97</v>
       </c>
       <c r="F72" t="n">
-        <v>194.62</v>
+        <v>306.67</v>
       </c>
       <c r="G72" t="n">
-        <v>2553.59</v>
+        <v>2665.64</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -4609,10 +4609,10 @@
         <v>446.73</v>
       </c>
       <c r="F73" t="n">
-        <v>36.85</v>
+        <v>58.07</v>
       </c>
       <c r="G73" t="n">
-        <v>483.58</v>
+        <v>504.8</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -4653,10 +4653,10 @@
         <v>3417.62</v>
       </c>
       <c r="F74" t="n">
-        <v>281.95</v>
+        <v>444.29</v>
       </c>
       <c r="G74" t="n">
-        <v>3699.57</v>
+        <v>3861.91</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -4697,10 +4697,10 @@
         <v>3203.69</v>
       </c>
       <c r="F75" t="n">
-        <v>264.3</v>
+        <v>416.48</v>
       </c>
       <c r="G75" t="n">
-        <v>3467.99</v>
+        <v>3620.17</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -4741,10 +4741,10 @@
         <v>4520.95</v>
       </c>
       <c r="F76" t="n">
-        <v>372.98</v>
+        <v>587.72</v>
       </c>
       <c r="G76" t="n">
-        <v>4893.93</v>
+        <v>5108.67</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
@@ -4785,10 +4785,10 @@
         <v>5569.38</v>
       </c>
       <c r="F77" t="n">
-        <v>459.47</v>
+        <v>724.02</v>
       </c>
       <c r="G77" t="n">
-        <v>6028.85</v>
+        <v>6293.4</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -4826,10 +4826,10 @@
         <v>3264.4</v>
       </c>
       <c r="F78" t="n">
-        <v>269.31</v>
+        <v>424.37</v>
       </c>
       <c r="G78" t="n">
-        <v>3533.72</v>
+        <v>3688.77</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -4870,10 +4870,10 @@
         <v>5283.46</v>
       </c>
       <c r="F79" t="n">
-        <v>435.89</v>
+        <v>686.85</v>
       </c>
       <c r="G79" t="n">
-        <v>5719.35</v>
+        <v>5970.31</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -4911,10 +4911,10 @@
         <v>4949.53</v>
       </c>
       <c r="F80" t="n">
-        <v>408.34</v>
+        <v>643.4400000000001</v>
       </c>
       <c r="G80" t="n">
-        <v>5357.86</v>
+        <v>5592.97</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -4955,10 +4955,10 @@
         <v>3623.39</v>
       </c>
       <c r="F81" t="n">
-        <v>298.93</v>
+        <v>471.04</v>
       </c>
       <c r="G81" t="n">
-        <v>3922.32</v>
+        <v>4094.43</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -4996,10 +4996,10 @@
         <v>1057.02</v>
       </c>
       <c r="F82" t="n">
-        <v>87.20999999999999</v>
+        <v>137.41</v>
       </c>
       <c r="G82" t="n">
-        <v>1144.23</v>
+        <v>1194.43</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
@@ -5040,10 +5040,10 @@
         <v>568.79</v>
       </c>
       <c r="F83" t="n">
-        <v>46.93</v>
+        <v>73.94</v>
       </c>
       <c r="G83" t="n">
-        <v>615.72</v>
+        <v>642.73</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -5084,10 +5084,10 @@
         <v>1869.95</v>
       </c>
       <c r="F84" t="n">
-        <v>154.27</v>
+        <v>243.09</v>
       </c>
       <c r="G84" t="n">
-        <v>2024.22</v>
+        <v>2113.04</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -5128,10 +5128,10 @@
         <v>987.33</v>
       </c>
       <c r="F85" t="n">
-        <v>81.45</v>
+        <v>128.35</v>
       </c>
       <c r="G85" t="n">
-        <v>1068.79</v>
+        <v>1115.68</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -5169,10 +5169,10 @@
         <v>2617.92</v>
       </c>
       <c r="F86" t="n">
-        <v>215.98</v>
+        <v>340.33</v>
       </c>
       <c r="G86" t="n">
-        <v>2833.9</v>
+        <v>2958.25</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -5213,10 +5213,10 @@
         <v>3141.51</v>
       </c>
       <c r="F87" t="n">
-        <v>259.17</v>
+        <v>408.4</v>
       </c>
       <c r="G87" t="n">
-        <v>3400.68</v>
+        <v>3549.91</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -5257,10 +5257,10 @@
         <v>1046.42</v>
       </c>
       <c r="F88" t="n">
-        <v>86.33</v>
+        <v>136.03</v>
       </c>
       <c r="G88" t="n">
-        <v>1132.75</v>
+        <v>1182.45</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
@@ -5301,10 +5301,10 @@
         <v>1420.41</v>
       </c>
       <c r="F89" t="n">
-        <v>117.19</v>
+        <v>184.65</v>
       </c>
       <c r="G89" t="n">
-        <v>1537.6</v>
+        <v>1605.06</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -5342,10 +5342,10 @@
         <v>4113.88</v>
       </c>
       <c r="F90" t="n">
-        <v>339.4</v>
+        <v>534.8</v>
       </c>
       <c r="G90" t="n">
-        <v>4453.28</v>
+        <v>4648.68</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -5386,10 +5386,10 @@
         <v>448.04</v>
       </c>
       <c r="F91" t="n">
-        <v>36.97</v>
+        <v>58.25</v>
       </c>
       <c r="G91" t="n">
-        <v>485</v>
+        <v>506.29</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -5493,10 +5493,10 @@
         <v>2449.71</v>
       </c>
       <c r="F2" t="n">
-        <v>202.1</v>
+        <v>318.46</v>
       </c>
       <c r="G2" t="n">
-        <v>2651.81</v>
+        <v>2768.17</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -5581,10 +5581,10 @@
         <v>3048.49</v>
       </c>
       <c r="F4" t="n">
-        <v>251.51</v>
+        <v>396.3</v>
       </c>
       <c r="G4" t="n">
-        <v>3300</v>
+        <v>3444.79</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -5622,10 +5622,10 @@
         <v>668.22</v>
       </c>
       <c r="F5" t="n">
-        <v>55.13</v>
+        <v>86.87</v>
       </c>
       <c r="G5" t="n">
-        <v>723.35</v>
+        <v>755.09</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -5666,10 +5666,10 @@
         <v>2868.48</v>
       </c>
       <c r="F6" t="n">
-        <v>236.65</v>
+        <v>372.9</v>
       </c>
       <c r="G6" t="n">
-        <v>3105.13</v>
+        <v>3241.38</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -5710,10 +5710,10 @@
         <v>2233.58</v>
       </c>
       <c r="F7" t="n">
-        <v>184.27</v>
+        <v>290.37</v>
       </c>
       <c r="G7" t="n">
-        <v>2417.85</v>
+        <v>2523.95</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -5754,10 +5754,10 @@
         <v>3048.5</v>
       </c>
       <c r="F8" t="n">
-        <v>251.5</v>
+        <v>396.31</v>
       </c>
       <c r="G8" t="n">
-        <v>3300</v>
+        <v>3444.81</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -5795,10 +5795,10 @@
         <v>1380.6</v>
       </c>
       <c r="F9" t="n">
-        <v>113.9</v>
+        <v>179.48</v>
       </c>
       <c r="G9" t="n">
-        <v>1494.5</v>
+        <v>1560.08</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -5836,10 +5836,10 @@
         <v>3048.5</v>
       </c>
       <c r="F10" t="n">
-        <v>251.5</v>
+        <v>396.31</v>
       </c>
       <c r="G10" t="n">
-        <v>3300</v>
+        <v>3444.81</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -5880,10 +5880,10 @@
         <v>2437.46</v>
       </c>
       <c r="F11" t="n">
-        <v>201.09</v>
+        <v>316.87</v>
       </c>
       <c r="G11" t="n">
-        <v>2638.55</v>
+        <v>2754.33</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         <v>3048.5</v>
       </c>
       <c r="F12" t="n">
-        <v>251.5</v>
+        <v>396.31</v>
       </c>
       <c r="G12" t="n">
-        <v>3300</v>
+        <v>3444.81</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -5965,10 +5965,10 @@
         <v>3048.49</v>
       </c>
       <c r="F13" t="n">
-        <v>251.5</v>
+        <v>396.3</v>
       </c>
       <c r="G13" t="n">
-        <v>3299.99</v>
+        <v>3444.79</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -6006,10 +6006,10 @@
         <v>1860.33</v>
       </c>
       <c r="F14" t="n">
-        <v>153.48</v>
+        <v>241.84</v>
       </c>
       <c r="G14" t="n">
-        <v>2013.81</v>
+        <v>2102.17</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -6047,10 +6047,10 @@
         <v>3048.5</v>
       </c>
       <c r="F15" t="n">
-        <v>251.5</v>
+        <v>396.31</v>
       </c>
       <c r="G15" t="n">
-        <v>3300</v>
+        <v>3444.81</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -6088,10 +6088,10 @@
         <v>3048.5</v>
       </c>
       <c r="F16" t="n">
-        <v>251.5</v>
+        <v>396.31</v>
       </c>
       <c r="G16" t="n">
-        <v>3300</v>
+        <v>3444.81</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -6132,10 +6132,10 @@
         <v>505.14</v>
       </c>
       <c r="F17" t="n">
-        <v>41.67</v>
+        <v>65.67</v>
       </c>
       <c r="G17" t="n">
-        <v>546.8099999999999</v>
+        <v>570.8099999999999</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -6217,10 +6217,10 @@
         <v>3048.5</v>
       </c>
       <c r="F19" t="n">
-        <v>251.5</v>
+        <v>396.31</v>
       </c>
       <c r="G19" t="n">
-        <v>3300</v>
+        <v>3444.81</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -6261,10 +6261,10 @@
         <v>2088.21</v>
       </c>
       <c r="F20" t="n">
-        <v>172.26</v>
+        <v>271.47</v>
       </c>
       <c r="G20" t="n">
-        <v>2260.47</v>
+        <v>2359.68</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -6305,10 +6305,10 @@
         <v>1880.91</v>
       </c>
       <c r="F21" t="n">
-        <v>155.16</v>
+        <v>244.52</v>
       </c>
       <c r="G21" t="n">
-        <v>2036.07</v>
+        <v>2125.43</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -6349,10 +6349,10 @@
         <v>3048.53</v>
       </c>
       <c r="F22" t="n">
-        <v>251.47</v>
+        <v>396.31</v>
       </c>
       <c r="G22" t="n">
-        <v>3300</v>
+        <v>3444.84</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -6393,10 +6393,10 @@
         <v>3048.51</v>
       </c>
       <c r="F23" t="n">
-        <v>251.49</v>
+        <v>396.31</v>
       </c>
       <c r="G23" t="n">
-        <v>3300</v>
+        <v>3444.82</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -6478,10 +6478,10 @@
         <v>666.78</v>
       </c>
       <c r="F25" t="n">
-        <v>55.01</v>
+        <v>86.68000000000001</v>
       </c>
       <c r="G25" t="n">
-        <v>721.79</v>
+        <v>753.46</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -6522,10 +6522,10 @@
         <v>1296.12</v>
       </c>
       <c r="F26" t="n">
-        <v>106.93</v>
+        <v>168.5</v>
       </c>
       <c r="G26" t="n">
-        <v>1403.05</v>
+        <v>1464.62</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -6563,10 +6563,10 @@
         <v>1541.68</v>
       </c>
       <c r="F27" t="n">
-        <v>127.19</v>
+        <v>200.42</v>
       </c>
       <c r="G27" t="n">
-        <v>1668.87</v>
+        <v>1742.1</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -6651,10 +6651,10 @@
         <v>1552.43</v>
       </c>
       <c r="F29" t="n">
-        <v>127.9</v>
+        <v>201.82</v>
       </c>
       <c r="G29" t="n">
-        <v>1680.33</v>
+        <v>1754.25</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -6695,10 +6695,10 @@
         <v>1373.69</v>
       </c>
       <c r="F30" t="n">
-        <v>113.33</v>
+        <v>178.58</v>
       </c>
       <c r="G30" t="n">
-        <v>1487.02</v>
+        <v>1552.27</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -6739,10 +6739,10 @@
         <v>2655.69</v>
       </c>
       <c r="F31" t="n">
-        <v>219.07</v>
+        <v>345.24</v>
       </c>
       <c r="G31" t="n">
-        <v>2874.76</v>
+        <v>3000.93</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -6783,10 +6783,10 @@
         <v>950.23</v>
       </c>
       <c r="F32" t="n">
-        <v>78.39</v>
+        <v>123.53</v>
       </c>
       <c r="G32" t="n">
-        <v>1028.62</v>
+        <v>1073.76</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -6824,10 +6824,10 @@
         <v>870.63</v>
       </c>
       <c r="F33" t="n">
-        <v>71.83</v>
+        <v>113.18</v>
       </c>
       <c r="G33" t="n">
-        <v>942.46</v>
+        <v>983.8099999999999</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -6865,10 +6865,10 @@
         <v>1392.75</v>
       </c>
       <c r="F34" t="n">
-        <v>114.9</v>
+        <v>181.06</v>
       </c>
       <c r="G34" t="n">
-        <v>1507.65</v>
+        <v>1573.81</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -6906,10 +6906,10 @@
         <v>1840.5</v>
       </c>
       <c r="F35" t="n">
-        <v>151.84</v>
+        <v>239.27</v>
       </c>
       <c r="G35" t="n">
-        <v>1992.34</v>
+        <v>2079.77</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -6947,10 +6947,10 @@
         <v>149</v>
       </c>
       <c r="F36" t="n">
-        <v>12.29</v>
+        <v>19.37</v>
       </c>
       <c r="G36" t="n">
-        <v>161.29</v>
+        <v>168.37</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -15221,13 +15221,13 @@
         <v>15500</v>
       </c>
       <c r="F2" t="n">
-        <v>1278.75</v>
+        <v>2015</v>
       </c>
       <c r="G2" t="n">
-        <v>16778.75</v>
+        <v>17515</v>
       </c>
       <c r="H2" t="n">
-        <v>16778.75</v>
+        <v>17515</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -15263,13 +15263,13 @@
         <v>12750</v>
       </c>
       <c r="F3" t="n">
-        <v>1051.88</v>
+        <v>1657.5</v>
       </c>
       <c r="G3" t="n">
-        <v>13801.88</v>
+        <v>14407.5</v>
       </c>
       <c r="H3" t="n">
-        <v>13801.88</v>
+        <v>14407.5</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -15305,13 +15305,13 @@
         <v>9600</v>
       </c>
       <c r="F4" t="n">
-        <v>792</v>
+        <v>1248</v>
       </c>
       <c r="G4" t="n">
-        <v>10392</v>
+        <v>10848</v>
       </c>
       <c r="H4" t="n">
-        <v>10392</v>
+        <v>10848</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -15347,13 +15347,13 @@
         <v>18200</v>
       </c>
       <c r="F5" t="n">
-        <v>1501.5</v>
+        <v>2366</v>
       </c>
       <c r="G5" t="n">
-        <v>19701.5</v>
+        <v>20566</v>
       </c>
       <c r="H5" t="n">
-        <v>19701.5</v>
+        <v>20566</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -15389,13 +15389,13 @@
         <v>8600</v>
       </c>
       <c r="F6" t="n">
-        <v>709.5</v>
+        <v>1118</v>
       </c>
       <c r="G6" t="n">
-        <v>9309.5</v>
+        <v>9718</v>
       </c>
       <c r="H6" t="n">
-        <v>9309.5</v>
+        <v>9718</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -15431,13 +15431,13 @@
         <v>11800</v>
       </c>
       <c r="F7" t="n">
-        <v>973.5</v>
+        <v>1534</v>
       </c>
       <c r="G7" t="n">
-        <v>12773.5</v>
+        <v>13334</v>
       </c>
       <c r="H7" t="n">
-        <v>12773.5</v>
+        <v>13334</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -15473,13 +15473,13 @@
         <v>9200</v>
       </c>
       <c r="F8" t="n">
-        <v>759</v>
+        <v>1196</v>
       </c>
       <c r="G8" t="n">
-        <v>9959</v>
+        <v>10396</v>
       </c>
       <c r="H8" t="n">
-        <v>9959</v>
+        <v>10396</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -15515,13 +15515,13 @@
         <v>7500</v>
       </c>
       <c r="F9" t="n">
-        <v>618.75</v>
+        <v>975</v>
       </c>
       <c r="G9" t="n">
-        <v>8118.75</v>
+        <v>8475</v>
       </c>
       <c r="H9" t="n">
-        <v>8118.75</v>
+        <v>8475</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -15557,13 +15557,13 @@
         <v>22500</v>
       </c>
       <c r="F10" t="n">
-        <v>1856.25</v>
+        <v>2925</v>
       </c>
       <c r="G10" t="n">
-        <v>24356.25</v>
+        <v>25425</v>
       </c>
       <c r="H10" t="n">
-        <v>24356.25</v>
+        <v>25425</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -15599,13 +15599,13 @@
         <v>14200</v>
       </c>
       <c r="F11" t="n">
-        <v>1171.5</v>
+        <v>1846</v>
       </c>
       <c r="G11" t="n">
-        <v>15371.5</v>
+        <v>16046</v>
       </c>
       <c r="H11" t="n">
-        <v>15371.5</v>
+        <v>16046</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -15641,13 +15641,13 @@
         <v>11500</v>
       </c>
       <c r="F12" t="n">
-        <v>948.75</v>
+        <v>1495</v>
       </c>
       <c r="G12" t="n">
-        <v>12448.75</v>
+        <v>12995</v>
       </c>
       <c r="H12" t="n">
-        <v>12448.75</v>
+        <v>12995</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -15683,13 +15683,13 @@
         <v>9200</v>
       </c>
       <c r="F13" t="n">
-        <v>759</v>
+        <v>1196</v>
       </c>
       <c r="G13" t="n">
-        <v>9959</v>
+        <v>10396</v>
       </c>
       <c r="H13" t="n">
-        <v>9959</v>
+        <v>10396</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -15725,13 +15725,13 @@
         <v>16800</v>
       </c>
       <c r="F14" t="n">
-        <v>1386</v>
+        <v>2184</v>
       </c>
       <c r="G14" t="n">
-        <v>18186</v>
+        <v>18984</v>
       </c>
       <c r="H14" t="n">
-        <v>18186</v>
+        <v>18984</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -15767,13 +15767,13 @@
         <v>5200</v>
       </c>
       <c r="F15" t="n">
-        <v>429</v>
+        <v>676</v>
       </c>
       <c r="G15" t="n">
-        <v>5629</v>
+        <v>5876</v>
       </c>
       <c r="H15" t="n">
-        <v>5629</v>
+        <v>5876</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -15809,13 +15809,13 @@
         <v>7800</v>
       </c>
       <c r="F16" t="n">
-        <v>643.5</v>
+        <v>1014</v>
       </c>
       <c r="G16" t="n">
-        <v>8443.5</v>
+        <v>8814</v>
       </c>
       <c r="H16" t="n">
-        <v>8443.5</v>
+        <v>8814</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -15851,13 +15851,13 @@
         <v>6200</v>
       </c>
       <c r="F17" t="n">
-        <v>511.5</v>
+        <v>806</v>
       </c>
       <c r="G17" t="n">
-        <v>6711.5</v>
+        <v>7006</v>
       </c>
       <c r="H17" t="n">
-        <v>6711.5</v>
+        <v>7006</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -15893,13 +15893,13 @@
         <v>3950</v>
       </c>
       <c r="F18" t="n">
-        <v>325.88</v>
+        <v>513.5</v>
       </c>
       <c r="G18" t="n">
-        <v>4275.88</v>
+        <v>4463.5</v>
       </c>
       <c r="H18" t="n">
-        <v>4275.88</v>
+        <v>4463.5</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -15935,13 +15935,13 @@
         <v>9600</v>
       </c>
       <c r="F19" t="n">
-        <v>792</v>
+        <v>1248</v>
       </c>
       <c r="G19" t="n">
-        <v>10392</v>
+        <v>10848</v>
       </c>
       <c r="H19" t="n">
-        <v>10392</v>
+        <v>10848</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -15977,13 +15977,13 @@
         <v>8500</v>
       </c>
       <c r="F20" t="n">
-        <v>701.25</v>
+        <v>1105</v>
       </c>
       <c r="G20" t="n">
-        <v>9201.25</v>
+        <v>9605</v>
       </c>
       <c r="H20" t="n">
-        <v>9201.25</v>
+        <v>9605</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -16019,13 +16019,13 @@
         <v>6200</v>
       </c>
       <c r="F21" t="n">
-        <v>511.5</v>
+        <v>806</v>
       </c>
       <c r="G21" t="n">
-        <v>6711.5</v>
+        <v>7006</v>
       </c>
       <c r="H21" t="n">
-        <v>6711.5</v>
+        <v>7006</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -16061,13 +16061,13 @@
         <v>13500</v>
       </c>
       <c r="F22" t="n">
-        <v>1113.75</v>
+        <v>1755</v>
       </c>
       <c r="G22" t="n">
-        <v>14613.75</v>
+        <v>15255</v>
       </c>
       <c r="H22" t="n">
-        <v>14613.75</v>
+        <v>15255</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
@@ -16103,16 +16103,16 @@
         <v>19800</v>
       </c>
       <c r="F23" t="n">
-        <v>1633.5</v>
+        <v>2574</v>
       </c>
       <c r="G23" t="n">
-        <v>21433.5</v>
+        <v>22374</v>
       </c>
       <c r="H23" t="n">
         <v>10000</v>
       </c>
       <c r="I23" t="n">
-        <v>11433.5</v>
+        <v>12374</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -16145,16 +16145,16 @@
         <v>8200</v>
       </c>
       <c r="F24" t="n">
-        <v>676.5</v>
+        <v>1066</v>
       </c>
       <c r="G24" t="n">
-        <v>8876.5</v>
+        <v>9266</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>8876.5</v>
+        <v>9266</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -16187,16 +16187,16 @@
         <v>11500</v>
       </c>
       <c r="F25" t="n">
-        <v>948.75</v>
+        <v>1495</v>
       </c>
       <c r="G25" t="n">
-        <v>12448.75</v>
+        <v>12995</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>12448.75</v>
+        <v>12995</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -16229,16 +16229,16 @@
         <v>7800</v>
       </c>
       <c r="F26" t="n">
-        <v>643.5</v>
+        <v>1014</v>
       </c>
       <c r="G26" t="n">
-        <v>8443.5</v>
+        <v>8814</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>8443.5</v>
+        <v>8814</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -16324,7 +16324,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>16778.75</v>
+        <v>17515</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -16364,7 +16364,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>13801.88</v>
+        <v>14407.5</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -16404,7 +16404,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>10392</v>
+        <v>10848</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -16444,7 +16444,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>19701.5</v>
+        <v>20566</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -16484,7 +16484,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>9309.5</v>
+        <v>9718</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -16524,7 +16524,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>12773.5</v>
+        <v>13334</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -16564,7 +16564,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>9959</v>
+        <v>10396</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -16604,7 +16604,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>8118.75</v>
+        <v>8475</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -16644,7 +16644,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>24356.25</v>
+        <v>25425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -16684,7 +16684,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>15371.5</v>
+        <v>16046</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -16724,7 +16724,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>12448.75</v>
+        <v>12995</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -16764,7 +16764,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>9959</v>
+        <v>10396</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -16804,7 +16804,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>18186</v>
+        <v>18984</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -16844,7 +16844,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5629</v>
+        <v>5876</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -16884,7 +16884,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>8443.5</v>
+        <v>8814</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -16924,7 +16924,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6711.5</v>
+        <v>7006</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -16964,7 +16964,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4275.88</v>
+        <v>4463.5</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -17004,7 +17004,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>10392</v>
+        <v>10848</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -17044,7 +17044,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>9201.25</v>
+        <v>9605</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -17084,7 +17084,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6711.5</v>
+        <v>7006</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -17124,7 +17124,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>14613.75</v>
+        <v>15255</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>

--- a/ArgoBooks/Resources/SampleCompanyData.xlsx
+++ b/ArgoBooks/Resources/SampleCompanyData.xlsx
@@ -6244,7 +6244,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7298,7 +7298,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="E4" t="n">
